--- a/portal2027-plantilla-importar-estudiantes.xlsx
+++ b/portal2027-plantilla-importar-estudiantes.xlsx
@@ -447,20 +447,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K300"/>
+  <dimension ref="A1:L300"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18.83203125" customWidth="1" min="1" max="1"/>
-    <col width="18.83203125" customWidth="1" min="2" max="2"/>
-    <col width="20.83203125" customWidth="1" min="3" max="3"/>
+    <col width="18.8" customWidth="1" min="1" max="1"/>
+    <col width="18.8" customWidth="1" min="2" max="2"/>
+    <col width="20.8" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="8.83203125" customWidth="1" min="5" max="5"/>
-    <col width="10.83203125" customWidth="1" min="6" max="6"/>
-    <col width="13.83203125" customWidth="1" min="7" max="7"/>
-    <col width="34.83203125" customWidth="1" min="8" max="8"/>
-    <col width="22.83203125" customWidth="1" min="9" max="9"/>
-    <col width="32.83203125" customWidth="1" min="10" max="10"/>
-    <col width="10.83203125" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="8.800000000000001" customWidth="1" min="6" max="6"/>
+    <col width="10.8" customWidth="1" min="7" max="7"/>
+    <col width="13.8" customWidth="1" min="8" max="8"/>
+    <col width="34.8" customWidth="1" min="9" max="9"/>
+    <col width="22.8" customWidth="1" min="10" max="10"/>
+    <col width="32.8" customWidth="1" min="11" max="11"/>
+    <col width="10.8" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -486,35 +487,40 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>sexo</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>grado</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>seccion</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>anio_lectivo</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>correo_estudiante</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>nombre_acudiente</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>telefono_acudiente</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>estado</t>
         </is>
@@ -543,35 +549,40 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>2027</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>ana.perez.prueba@example.com</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>Carmen Gómez</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>6000-0001 / 6500-0002</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>activo</t>
         </is>
@@ -600,30 +611,35 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>2027</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>luis.rodriguez.prueba@example.com</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>Jorge Rodríguez</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>6000-0002; 6500-0003 (trabajo)</t>
         </is>
@@ -652,30 +668,35 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>2027</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>Rosa Ruiz</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>6000-0003</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>activo</t>
         </is>
@@ -704,15 +725,20 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>2027</t>
         </is>
@@ -1604,6 +1630,11 @@
       <c r="D300" s="1" t="n"/>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="E2:E300" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Sexo" error="Elija Femenino o Masculino" type="list">
+      <formula1>"Femenino,Masculino"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1614,7 +1645,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22.83203125" customWidth="1" min="1" max="1"/>
@@ -1765,7 +1796,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>grado</t>
+          <t>sexo</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1775,19 +1806,19 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Solo el número del grado (uno o dos dígitos).</t>
+          <t>Elija Femenino o Masculino de la lista (también vale F o M). Si el estudiante ya tiene el sexo registrado, puede dejarla vacía.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>Femenino</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>seccion</t>
+          <t>grado</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1797,19 +1828,19 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Solo la letra de la sección. Grado 9 + sección C = grupo 9C.</t>
+          <t>Solo el número del grado (uno o dos dígitos).</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>9</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>anio_lectivo</t>
+          <t>seccion</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1819,41 +1850,41 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Año con cuatro cifras. Debe existir en Años lectivos.</t>
+          <t>Solo la letra de la sección. Grado 9 + sección C = grupo 9C.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>C</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>correo_estudiante</t>
+          <t>anio_lectivo</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Correo propio del estudiante, para invitarlo. No puede repetirse.</t>
+          <t>Año con cuatro cifras. Debe existir en Años lectivos.</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>ana@example.com</t>
+          <t>2027</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>nombre_acudiente</t>
+          <t>correo_estudiante</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1863,19 +1894,19 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Nombre del acudiente.</t>
+          <t>Correo propio del estudiante, para invitarlo. No puede repetirse.</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Carmen Gómez</t>
+          <t>ana@example.com</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>telefono_acudiente</t>
+          <t>nombre_acudiente</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1885,32 +1916,54 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Uno o varios teléfonos en la misma celda, separados por « / » o «; ».</t>
+          <t>Nombre del acudiente.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>6000-0001 / 6500-0002</t>
+          <t>Carmen Gómez</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>telefono_acudiente</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Uno o varios teléfonos en la misma celda, separados por « / » o «; ».</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>6000-0001 / 6500-0002</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>estado</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>Estado de la matrícula. Vacío = activo.</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>activo</t>
         </is>

--- a/portal2027-plantilla-importar-estudiantes.xlsx
+++ b/portal2027-plantilla-importar-estudiantes.xlsx
@@ -447,21 +447,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L300"/>
+  <dimension ref="A1:K300"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.8" customWidth="1" min="1" max="1"/>
-    <col width="18.8" customWidth="1" min="2" max="2"/>
-    <col width="20.8" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="8.800000000000001" customWidth="1" min="6" max="6"/>
-    <col width="10.8" customWidth="1" min="7" max="7"/>
-    <col width="13.8" customWidth="1" min="8" max="8"/>
-    <col width="34.8" customWidth="1" min="9" max="9"/>
-    <col width="22.8" customWidth="1" min="10" max="10"/>
-    <col width="32.8" customWidth="1" min="11" max="11"/>
-    <col width="10.8" customWidth="1" min="12" max="12"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="8.800000000000001" customWidth="1" min="5" max="5"/>
+    <col width="10.8" customWidth="1" min="6" max="6"/>
+    <col width="13.8" customWidth="1" min="7" max="7"/>
+    <col width="34.8" customWidth="1" min="8" max="8"/>
+    <col width="22.8" customWidth="1" min="9" max="9"/>
+    <col width="32.8" customWidth="1" min="10" max="10"/>
+    <col width="10.8" customWidth="1" min="11" max="11"/>
+    <col width="8.800000000000001" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -477,50 +477,45 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>apellidos</t>
+          <t>cedula</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>cedula</t>
+          <t>sexo</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>sexo</t>
+          <t>grado</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>grado</t>
+          <t>seccion</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>seccion</t>
+          <t>anio_lectivo</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>anio_lectivo</t>
+          <t>correo_estudiante</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>correo_estudiante</t>
+          <t>nombre_acudiente</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>nombre_acudiente</t>
+          <t>telefono_acudiente</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
-        <is>
-          <t>telefono_acudiente</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
         <is>
           <t>estado</t>
         </is>
@@ -534,55 +529,50 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Ana María</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Pérez Gómez</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
+          <t>Pérez Gómez, Ana María</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
         <is>
           <t>8-123-456</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>ana.perez.prueba@example.com</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>ana.perez.prueba@example.com</t>
+          <t>Carmen Gómez</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Carmen Gómez</t>
+          <t>6000-0001 / 6500-0002</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
-        <is>
-          <t>6000-0001 / 6500-0002</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
         <is>
           <t>activo</t>
         </is>
@@ -596,50 +586,45 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Luis Carlos</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Rodríguez Díaz</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
+          <t>Rodríguez Díaz, Luis Carlos</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
         <is>
           <t>4-567-890</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>luis.rodriguez.prueba@example.com</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>luis.rodriguez.prueba@example.com</t>
+          <t>Jorge Rodríguez</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
-        <is>
-          <t>Jorge Rodríguez</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
         <is>
           <t>6000-0002; 6500-0003 (trabajo)</t>
         </is>
@@ -653,50 +638,45 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>María José</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Castillo Ruiz</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="inlineStr">
+          <t>Castillo Ruiz, María José</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
         <is>
           <t>E-8-123456</t>
         </is>
       </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
           <t>2027</t>
         </is>
       </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Rosa Ruiz</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Rosa Ruiz</t>
+          <t>6000-0003</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
-        <is>
-          <t>6000-0003</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
         <is>
           <t>activo</t>
         </is>
@@ -710,928 +690,923 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Pedro</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Santos Vega</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="inlineStr">
+          <t>Santos Vega, Pedro</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
         <is>
           <t>PE-12-345</t>
         </is>
       </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
           <t>2027</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="D6" s="1" t="n"/>
+      <c r="C6" s="1" t="n"/>
     </row>
     <row r="7">
-      <c r="D7" s="1" t="n"/>
+      <c r="C7" s="1" t="n"/>
     </row>
     <row r="8">
-      <c r="D8" s="1" t="n"/>
+      <c r="C8" s="1" t="n"/>
     </row>
     <row r="9">
-      <c r="D9" s="1" t="n"/>
+      <c r="C9" s="1" t="n"/>
     </row>
     <row r="10">
-      <c r="D10" s="1" t="n"/>
+      <c r="C10" s="1" t="n"/>
     </row>
     <row r="11">
-      <c r="D11" s="1" t="n"/>
+      <c r="C11" s="1" t="n"/>
     </row>
     <row r="12">
-      <c r="D12" s="1" t="n"/>
+      <c r="C12" s="1" t="n"/>
     </row>
     <row r="13">
-      <c r="D13" s="1" t="n"/>
+      <c r="C13" s="1" t="n"/>
     </row>
     <row r="14">
-      <c r="D14" s="1" t="n"/>
+      <c r="C14" s="1" t="n"/>
     </row>
     <row r="15">
-      <c r="D15" s="1" t="n"/>
+      <c r="C15" s="1" t="n"/>
     </row>
     <row r="16">
-      <c r="D16" s="1" t="n"/>
+      <c r="C16" s="1" t="n"/>
     </row>
     <row r="17">
-      <c r="D17" s="1" t="n"/>
+      <c r="C17" s="1" t="n"/>
     </row>
     <row r="18">
-      <c r="D18" s="1" t="n"/>
+      <c r="C18" s="1" t="n"/>
     </row>
     <row r="19">
-      <c r="D19" s="1" t="n"/>
+      <c r="C19" s="1" t="n"/>
     </row>
     <row r="20">
-      <c r="D20" s="1" t="n"/>
+      <c r="C20" s="1" t="n"/>
     </row>
     <row r="21">
-      <c r="D21" s="1" t="n"/>
+      <c r="C21" s="1" t="n"/>
     </row>
     <row r="22">
-      <c r="D22" s="1" t="n"/>
+      <c r="C22" s="1" t="n"/>
     </row>
     <row r="23">
-      <c r="D23" s="1" t="n"/>
+      <c r="C23" s="1" t="n"/>
     </row>
     <row r="24">
-      <c r="D24" s="1" t="n"/>
+      <c r="C24" s="1" t="n"/>
     </row>
     <row r="25">
-      <c r="D25" s="1" t="n"/>
+      <c r="C25" s="1" t="n"/>
     </row>
     <row r="26">
-      <c r="D26" s="1" t="n"/>
+      <c r="C26" s="1" t="n"/>
     </row>
     <row r="27">
-      <c r="D27" s="1" t="n"/>
+      <c r="C27" s="1" t="n"/>
     </row>
     <row r="28">
-      <c r="D28" s="1" t="n"/>
+      <c r="C28" s="1" t="n"/>
     </row>
     <row r="29">
-      <c r="D29" s="1" t="n"/>
+      <c r="C29" s="1" t="n"/>
     </row>
     <row r="30">
-      <c r="D30" s="1" t="n"/>
+      <c r="C30" s="1" t="n"/>
     </row>
     <row r="31">
-      <c r="D31" s="1" t="n"/>
+      <c r="C31" s="1" t="n"/>
     </row>
     <row r="32">
-      <c r="D32" s="1" t="n"/>
+      <c r="C32" s="1" t="n"/>
     </row>
     <row r="33">
-      <c r="D33" s="1" t="n"/>
+      <c r="C33" s="1" t="n"/>
     </row>
     <row r="34">
-      <c r="D34" s="1" t="n"/>
+      <c r="C34" s="1" t="n"/>
     </row>
     <row r="35">
-      <c r="D35" s="1" t="n"/>
+      <c r="C35" s="1" t="n"/>
     </row>
     <row r="36">
-      <c r="D36" s="1" t="n"/>
+      <c r="C36" s="1" t="n"/>
     </row>
     <row r="37">
-      <c r="D37" s="1" t="n"/>
+      <c r="C37" s="1" t="n"/>
     </row>
     <row r="38">
-      <c r="D38" s="1" t="n"/>
+      <c r="C38" s="1" t="n"/>
     </row>
     <row r="39">
-      <c r="D39" s="1" t="n"/>
+      <c r="C39" s="1" t="n"/>
     </row>
     <row r="40">
-      <c r="D40" s="1" t="n"/>
+      <c r="C40" s="1" t="n"/>
     </row>
     <row r="41">
-      <c r="D41" s="1" t="n"/>
+      <c r="C41" s="1" t="n"/>
     </row>
     <row r="42">
-      <c r="D42" s="1" t="n"/>
+      <c r="C42" s="1" t="n"/>
     </row>
     <row r="43">
-      <c r="D43" s="1" t="n"/>
+      <c r="C43" s="1" t="n"/>
     </row>
     <row r="44">
-      <c r="D44" s="1" t="n"/>
+      <c r="C44" s="1" t="n"/>
     </row>
     <row r="45">
-      <c r="D45" s="1" t="n"/>
+      <c r="C45" s="1" t="n"/>
     </row>
     <row r="46">
-      <c r="D46" s="1" t="n"/>
+      <c r="C46" s="1" t="n"/>
     </row>
     <row r="47">
-      <c r="D47" s="1" t="n"/>
+      <c r="C47" s="1" t="n"/>
     </row>
     <row r="48">
-      <c r="D48" s="1" t="n"/>
+      <c r="C48" s="1" t="n"/>
     </row>
     <row r="49">
-      <c r="D49" s="1" t="n"/>
+      <c r="C49" s="1" t="n"/>
     </row>
     <row r="50">
-      <c r="D50" s="1" t="n"/>
+      <c r="C50" s="1" t="n"/>
     </row>
     <row r="51">
-      <c r="D51" s="1" t="n"/>
+      <c r="C51" s="1" t="n"/>
     </row>
     <row r="52">
-      <c r="D52" s="1" t="n"/>
+      <c r="C52" s="1" t="n"/>
     </row>
     <row r="53">
-      <c r="D53" s="1" t="n"/>
+      <c r="C53" s="1" t="n"/>
     </row>
     <row r="54">
-      <c r="D54" s="1" t="n"/>
+      <c r="C54" s="1" t="n"/>
     </row>
     <row r="55">
-      <c r="D55" s="1" t="n"/>
+      <c r="C55" s="1" t="n"/>
     </row>
     <row r="56">
-      <c r="D56" s="1" t="n"/>
+      <c r="C56" s="1" t="n"/>
     </row>
     <row r="57">
-      <c r="D57" s="1" t="n"/>
+      <c r="C57" s="1" t="n"/>
     </row>
     <row r="58">
-      <c r="D58" s="1" t="n"/>
+      <c r="C58" s="1" t="n"/>
     </row>
     <row r="59">
-      <c r="D59" s="1" t="n"/>
+      <c r="C59" s="1" t="n"/>
     </row>
     <row r="60">
-      <c r="D60" s="1" t="n"/>
+      <c r="C60" s="1" t="n"/>
     </row>
     <row r="61">
-      <c r="D61" s="1" t="n"/>
+      <c r="C61" s="1" t="n"/>
     </row>
     <row r="62">
-      <c r="D62" s="1" t="n"/>
+      <c r="C62" s="1" t="n"/>
     </row>
     <row r="63">
-      <c r="D63" s="1" t="n"/>
+      <c r="C63" s="1" t="n"/>
     </row>
     <row r="64">
-      <c r="D64" s="1" t="n"/>
+      <c r="C64" s="1" t="n"/>
     </row>
     <row r="65">
-      <c r="D65" s="1" t="n"/>
+      <c r="C65" s="1" t="n"/>
     </row>
     <row r="66">
-      <c r="D66" s="1" t="n"/>
+      <c r="C66" s="1" t="n"/>
     </row>
     <row r="67">
-      <c r="D67" s="1" t="n"/>
+      <c r="C67" s="1" t="n"/>
     </row>
     <row r="68">
-      <c r="D68" s="1" t="n"/>
+      <c r="C68" s="1" t="n"/>
     </row>
     <row r="69">
-      <c r="D69" s="1" t="n"/>
+      <c r="C69" s="1" t="n"/>
     </row>
     <row r="70">
-      <c r="D70" s="1" t="n"/>
+      <c r="C70" s="1" t="n"/>
     </row>
     <row r="71">
-      <c r="D71" s="1" t="n"/>
+      <c r="C71" s="1" t="n"/>
     </row>
     <row r="72">
-      <c r="D72" s="1" t="n"/>
+      <c r="C72" s="1" t="n"/>
     </row>
     <row r="73">
-      <c r="D73" s="1" t="n"/>
+      <c r="C73" s="1" t="n"/>
     </row>
     <row r="74">
-      <c r="D74" s="1" t="n"/>
+      <c r="C74" s="1" t="n"/>
     </row>
     <row r="75">
-      <c r="D75" s="1" t="n"/>
+      <c r="C75" s="1" t="n"/>
     </row>
     <row r="76">
-      <c r="D76" s="1" t="n"/>
+      <c r="C76" s="1" t="n"/>
     </row>
     <row r="77">
-      <c r="D77" s="1" t="n"/>
+      <c r="C77" s="1" t="n"/>
     </row>
     <row r="78">
-      <c r="D78" s="1" t="n"/>
+      <c r="C78" s="1" t="n"/>
     </row>
     <row r="79">
-      <c r="D79" s="1" t="n"/>
+      <c r="C79" s="1" t="n"/>
     </row>
     <row r="80">
-      <c r="D80" s="1" t="n"/>
+      <c r="C80" s="1" t="n"/>
     </row>
     <row r="81">
-      <c r="D81" s="1" t="n"/>
+      <c r="C81" s="1" t="n"/>
     </row>
     <row r="82">
-      <c r="D82" s="1" t="n"/>
+      <c r="C82" s="1" t="n"/>
     </row>
     <row r="83">
-      <c r="D83" s="1" t="n"/>
+      <c r="C83" s="1" t="n"/>
     </row>
     <row r="84">
-      <c r="D84" s="1" t="n"/>
+      <c r="C84" s="1" t="n"/>
     </row>
     <row r="85">
-      <c r="D85" s="1" t="n"/>
+      <c r="C85" s="1" t="n"/>
     </row>
     <row r="86">
-      <c r="D86" s="1" t="n"/>
+      <c r="C86" s="1" t="n"/>
     </row>
     <row r="87">
-      <c r="D87" s="1" t="n"/>
+      <c r="C87" s="1" t="n"/>
     </row>
     <row r="88">
-      <c r="D88" s="1" t="n"/>
+      <c r="C88" s="1" t="n"/>
     </row>
     <row r="89">
-      <c r="D89" s="1" t="n"/>
+      <c r="C89" s="1" t="n"/>
     </row>
     <row r="90">
-      <c r="D90" s="1" t="n"/>
+      <c r="C90" s="1" t="n"/>
     </row>
     <row r="91">
-      <c r="D91" s="1" t="n"/>
+      <c r="C91" s="1" t="n"/>
     </row>
     <row r="92">
-      <c r="D92" s="1" t="n"/>
+      <c r="C92" s="1" t="n"/>
     </row>
     <row r="93">
-      <c r="D93" s="1" t="n"/>
+      <c r="C93" s="1" t="n"/>
     </row>
     <row r="94">
-      <c r="D94" s="1" t="n"/>
+      <c r="C94" s="1" t="n"/>
     </row>
     <row r="95">
-      <c r="D95" s="1" t="n"/>
+      <c r="C95" s="1" t="n"/>
     </row>
     <row r="96">
-      <c r="D96" s="1" t="n"/>
+      <c r="C96" s="1" t="n"/>
     </row>
     <row r="97">
-      <c r="D97" s="1" t="n"/>
+      <c r="C97" s="1" t="n"/>
     </row>
     <row r="98">
-      <c r="D98" s="1" t="n"/>
+      <c r="C98" s="1" t="n"/>
     </row>
     <row r="99">
-      <c r="D99" s="1" t="n"/>
+      <c r="C99" s="1" t="n"/>
     </row>
     <row r="100">
-      <c r="D100" s="1" t="n"/>
+      <c r="C100" s="1" t="n"/>
     </row>
     <row r="101">
-      <c r="D101" s="1" t="n"/>
+      <c r="C101" s="1" t="n"/>
     </row>
     <row r="102">
-      <c r="D102" s="1" t="n"/>
+      <c r="C102" s="1" t="n"/>
     </row>
     <row r="103">
-      <c r="D103" s="1" t="n"/>
+      <c r="C103" s="1" t="n"/>
     </row>
     <row r="104">
-      <c r="D104" s="1" t="n"/>
+      <c r="C104" s="1" t="n"/>
     </row>
     <row r="105">
-      <c r="D105" s="1" t="n"/>
+      <c r="C105" s="1" t="n"/>
     </row>
     <row r="106">
-      <c r="D106" s="1" t="n"/>
+      <c r="C106" s="1" t="n"/>
     </row>
     <row r="107">
-      <c r="D107" s="1" t="n"/>
+      <c r="C107" s="1" t="n"/>
     </row>
     <row r="108">
-      <c r="D108" s="1" t="n"/>
+      <c r="C108" s="1" t="n"/>
     </row>
     <row r="109">
-      <c r="D109" s="1" t="n"/>
+      <c r="C109" s="1" t="n"/>
     </row>
     <row r="110">
-      <c r="D110" s="1" t="n"/>
+      <c r="C110" s="1" t="n"/>
     </row>
     <row r="111">
-      <c r="D111" s="1" t="n"/>
+      <c r="C111" s="1" t="n"/>
     </row>
     <row r="112">
-      <c r="D112" s="1" t="n"/>
+      <c r="C112" s="1" t="n"/>
     </row>
     <row r="113">
-      <c r="D113" s="1" t="n"/>
+      <c r="C113" s="1" t="n"/>
     </row>
     <row r="114">
-      <c r="D114" s="1" t="n"/>
+      <c r="C114" s="1" t="n"/>
     </row>
     <row r="115">
-      <c r="D115" s="1" t="n"/>
+      <c r="C115" s="1" t="n"/>
     </row>
     <row r="116">
-      <c r="D116" s="1" t="n"/>
+      <c r="C116" s="1" t="n"/>
     </row>
     <row r="117">
-      <c r="D117" s="1" t="n"/>
+      <c r="C117" s="1" t="n"/>
     </row>
     <row r="118">
-      <c r="D118" s="1" t="n"/>
+      <c r="C118" s="1" t="n"/>
     </row>
     <row r="119">
-      <c r="D119" s="1" t="n"/>
+      <c r="C119" s="1" t="n"/>
     </row>
     <row r="120">
-      <c r="D120" s="1" t="n"/>
+      <c r="C120" s="1" t="n"/>
     </row>
     <row r="121">
-      <c r="D121" s="1" t="n"/>
+      <c r="C121" s="1" t="n"/>
     </row>
     <row r="122">
-      <c r="D122" s="1" t="n"/>
+      <c r="C122" s="1" t="n"/>
     </row>
     <row r="123">
-      <c r="D123" s="1" t="n"/>
+      <c r="C123" s="1" t="n"/>
     </row>
     <row r="124">
-      <c r="D124" s="1" t="n"/>
+      <c r="C124" s="1" t="n"/>
     </row>
     <row r="125">
-      <c r="D125" s="1" t="n"/>
+      <c r="C125" s="1" t="n"/>
     </row>
     <row r="126">
-      <c r="D126" s="1" t="n"/>
+      <c r="C126" s="1" t="n"/>
     </row>
     <row r="127">
-      <c r="D127" s="1" t="n"/>
+      <c r="C127" s="1" t="n"/>
     </row>
     <row r="128">
-      <c r="D128" s="1" t="n"/>
+      <c r="C128" s="1" t="n"/>
     </row>
     <row r="129">
-      <c r="D129" s="1" t="n"/>
+      <c r="C129" s="1" t="n"/>
     </row>
     <row r="130">
-      <c r="D130" s="1" t="n"/>
+      <c r="C130" s="1" t="n"/>
     </row>
     <row r="131">
-      <c r="D131" s="1" t="n"/>
+      <c r="C131" s="1" t="n"/>
     </row>
     <row r="132">
-      <c r="D132" s="1" t="n"/>
+      <c r="C132" s="1" t="n"/>
     </row>
     <row r="133">
-      <c r="D133" s="1" t="n"/>
+      <c r="C133" s="1" t="n"/>
     </row>
     <row r="134">
-      <c r="D134" s="1" t="n"/>
+      <c r="C134" s="1" t="n"/>
     </row>
     <row r="135">
-      <c r="D135" s="1" t="n"/>
+      <c r="C135" s="1" t="n"/>
     </row>
     <row r="136">
-      <c r="D136" s="1" t="n"/>
+      <c r="C136" s="1" t="n"/>
     </row>
     <row r="137">
-      <c r="D137" s="1" t="n"/>
+      <c r="C137" s="1" t="n"/>
     </row>
     <row r="138">
-      <c r="D138" s="1" t="n"/>
+      <c r="C138" s="1" t="n"/>
     </row>
     <row r="139">
-      <c r="D139" s="1" t="n"/>
+      <c r="C139" s="1" t="n"/>
     </row>
     <row r="140">
-      <c r="D140" s="1" t="n"/>
+      <c r="C140" s="1" t="n"/>
     </row>
     <row r="141">
-      <c r="D141" s="1" t="n"/>
+      <c r="C141" s="1" t="n"/>
     </row>
     <row r="142">
-      <c r="D142" s="1" t="n"/>
+      <c r="C142" s="1" t="n"/>
     </row>
     <row r="143">
-      <c r="D143" s="1" t="n"/>
+      <c r="C143" s="1" t="n"/>
     </row>
     <row r="144">
-      <c r="D144" s="1" t="n"/>
+      <c r="C144" s="1" t="n"/>
     </row>
     <row r="145">
-      <c r="D145" s="1" t="n"/>
+      <c r="C145" s="1" t="n"/>
     </row>
     <row r="146">
-      <c r="D146" s="1" t="n"/>
+      <c r="C146" s="1" t="n"/>
     </row>
     <row r="147">
-      <c r="D147" s="1" t="n"/>
+      <c r="C147" s="1" t="n"/>
     </row>
     <row r="148">
-      <c r="D148" s="1" t="n"/>
+      <c r="C148" s="1" t="n"/>
     </row>
     <row r="149">
-      <c r="D149" s="1" t="n"/>
+      <c r="C149" s="1" t="n"/>
     </row>
     <row r="150">
-      <c r="D150" s="1" t="n"/>
+      <c r="C150" s="1" t="n"/>
     </row>
     <row r="151">
-      <c r="D151" s="1" t="n"/>
+      <c r="C151" s="1" t="n"/>
     </row>
     <row r="152">
-      <c r="D152" s="1" t="n"/>
+      <c r="C152" s="1" t="n"/>
     </row>
     <row r="153">
-      <c r="D153" s="1" t="n"/>
+      <c r="C153" s="1" t="n"/>
     </row>
     <row r="154">
-      <c r="D154" s="1" t="n"/>
+      <c r="C154" s="1" t="n"/>
     </row>
     <row r="155">
-      <c r="D155" s="1" t="n"/>
+      <c r="C155" s="1" t="n"/>
     </row>
     <row r="156">
-      <c r="D156" s="1" t="n"/>
+      <c r="C156" s="1" t="n"/>
     </row>
     <row r="157">
-      <c r="D157" s="1" t="n"/>
+      <c r="C157" s="1" t="n"/>
     </row>
     <row r="158">
-      <c r="D158" s="1" t="n"/>
+      <c r="C158" s="1" t="n"/>
     </row>
     <row r="159">
-      <c r="D159" s="1" t="n"/>
+      <c r="C159" s="1" t="n"/>
     </row>
     <row r="160">
-      <c r="D160" s="1" t="n"/>
+      <c r="C160" s="1" t="n"/>
     </row>
     <row r="161">
-      <c r="D161" s="1" t="n"/>
+      <c r="C161" s="1" t="n"/>
     </row>
     <row r="162">
-      <c r="D162" s="1" t="n"/>
+      <c r="C162" s="1" t="n"/>
     </row>
     <row r="163">
-      <c r="D163" s="1" t="n"/>
+      <c r="C163" s="1" t="n"/>
     </row>
     <row r="164">
-      <c r="D164" s="1" t="n"/>
+      <c r="C164" s="1" t="n"/>
     </row>
     <row r="165">
-      <c r="D165" s="1" t="n"/>
+      <c r="C165" s="1" t="n"/>
     </row>
     <row r="166">
-      <c r="D166" s="1" t="n"/>
+      <c r="C166" s="1" t="n"/>
     </row>
     <row r="167">
-      <c r="D167" s="1" t="n"/>
+      <c r="C167" s="1" t="n"/>
     </row>
     <row r="168">
-      <c r="D168" s="1" t="n"/>
+      <c r="C168" s="1" t="n"/>
     </row>
     <row r="169">
-      <c r="D169" s="1" t="n"/>
+      <c r="C169" s="1" t="n"/>
     </row>
     <row r="170">
-      <c r="D170" s="1" t="n"/>
+      <c r="C170" s="1" t="n"/>
     </row>
     <row r="171">
-      <c r="D171" s="1" t="n"/>
+      <c r="C171" s="1" t="n"/>
     </row>
     <row r="172">
-      <c r="D172" s="1" t="n"/>
+      <c r="C172" s="1" t="n"/>
     </row>
     <row r="173">
-      <c r="D173" s="1" t="n"/>
+      <c r="C173" s="1" t="n"/>
     </row>
     <row r="174">
-      <c r="D174" s="1" t="n"/>
+      <c r="C174" s="1" t="n"/>
     </row>
     <row r="175">
-      <c r="D175" s="1" t="n"/>
+      <c r="C175" s="1" t="n"/>
     </row>
     <row r="176">
-      <c r="D176" s="1" t="n"/>
+      <c r="C176" s="1" t="n"/>
     </row>
     <row r="177">
-      <c r="D177" s="1" t="n"/>
+      <c r="C177" s="1" t="n"/>
     </row>
     <row r="178">
-      <c r="D178" s="1" t="n"/>
+      <c r="C178" s="1" t="n"/>
     </row>
     <row r="179">
-      <c r="D179" s="1" t="n"/>
+      <c r="C179" s="1" t="n"/>
     </row>
     <row r="180">
-      <c r="D180" s="1" t="n"/>
+      <c r="C180" s="1" t="n"/>
     </row>
     <row r="181">
-      <c r="D181" s="1" t="n"/>
+      <c r="C181" s="1" t="n"/>
     </row>
     <row r="182">
-      <c r="D182" s="1" t="n"/>
+      <c r="C182" s="1" t="n"/>
     </row>
     <row r="183">
-      <c r="D183" s="1" t="n"/>
+      <c r="C183" s="1" t="n"/>
     </row>
     <row r="184">
-      <c r="D184" s="1" t="n"/>
+      <c r="C184" s="1" t="n"/>
     </row>
     <row r="185">
-      <c r="D185" s="1" t="n"/>
+      <c r="C185" s="1" t="n"/>
     </row>
     <row r="186">
-      <c r="D186" s="1" t="n"/>
+      <c r="C186" s="1" t="n"/>
     </row>
     <row r="187">
-      <c r="D187" s="1" t="n"/>
+      <c r="C187" s="1" t="n"/>
     </row>
     <row r="188">
-      <c r="D188" s="1" t="n"/>
+      <c r="C188" s="1" t="n"/>
     </row>
     <row r="189">
-      <c r="D189" s="1" t="n"/>
+      <c r="C189" s="1" t="n"/>
     </row>
     <row r="190">
-      <c r="D190" s="1" t="n"/>
+      <c r="C190" s="1" t="n"/>
     </row>
     <row r="191">
-      <c r="D191" s="1" t="n"/>
+      <c r="C191" s="1" t="n"/>
     </row>
     <row r="192">
-      <c r="D192" s="1" t="n"/>
+      <c r="C192" s="1" t="n"/>
     </row>
     <row r="193">
-      <c r="D193" s="1" t="n"/>
+      <c r="C193" s="1" t="n"/>
     </row>
     <row r="194">
-      <c r="D194" s="1" t="n"/>
+      <c r="C194" s="1" t="n"/>
     </row>
     <row r="195">
-      <c r="D195" s="1" t="n"/>
+      <c r="C195" s="1" t="n"/>
     </row>
     <row r="196">
-      <c r="D196" s="1" t="n"/>
+      <c r="C196" s="1" t="n"/>
     </row>
     <row r="197">
-      <c r="D197" s="1" t="n"/>
+      <c r="C197" s="1" t="n"/>
     </row>
     <row r="198">
-      <c r="D198" s="1" t="n"/>
+      <c r="C198" s="1" t="n"/>
     </row>
     <row r="199">
-      <c r="D199" s="1" t="n"/>
+      <c r="C199" s="1" t="n"/>
     </row>
     <row r="200">
-      <c r="D200" s="1" t="n"/>
+      <c r="C200" s="1" t="n"/>
     </row>
     <row r="201">
-      <c r="D201" s="1" t="n"/>
+      <c r="C201" s="1" t="n"/>
     </row>
     <row r="202">
-      <c r="D202" s="1" t="n"/>
+      <c r="C202" s="1" t="n"/>
     </row>
     <row r="203">
-      <c r="D203" s="1" t="n"/>
+      <c r="C203" s="1" t="n"/>
     </row>
     <row r="204">
-      <c r="D204" s="1" t="n"/>
+      <c r="C204" s="1" t="n"/>
     </row>
     <row r="205">
-      <c r="D205" s="1" t="n"/>
+      <c r="C205" s="1" t="n"/>
     </row>
     <row r="206">
-      <c r="D206" s="1" t="n"/>
+      <c r="C206" s="1" t="n"/>
     </row>
     <row r="207">
-      <c r="D207" s="1" t="n"/>
+      <c r="C207" s="1" t="n"/>
     </row>
     <row r="208">
-      <c r="D208" s="1" t="n"/>
+      <c r="C208" s="1" t="n"/>
     </row>
     <row r="209">
-      <c r="D209" s="1" t="n"/>
+      <c r="C209" s="1" t="n"/>
     </row>
     <row r="210">
-      <c r="D210" s="1" t="n"/>
+      <c r="C210" s="1" t="n"/>
     </row>
     <row r="211">
-      <c r="D211" s="1" t="n"/>
+      <c r="C211" s="1" t="n"/>
     </row>
     <row r="212">
-      <c r="D212" s="1" t="n"/>
+      <c r="C212" s="1" t="n"/>
     </row>
     <row r="213">
-      <c r="D213" s="1" t="n"/>
+      <c r="C213" s="1" t="n"/>
     </row>
     <row r="214">
-      <c r="D214" s="1" t="n"/>
+      <c r="C214" s="1" t="n"/>
     </row>
     <row r="215">
-      <c r="D215" s="1" t="n"/>
+      <c r="C215" s="1" t="n"/>
     </row>
     <row r="216">
-      <c r="D216" s="1" t="n"/>
+      <c r="C216" s="1" t="n"/>
     </row>
     <row r="217">
-      <c r="D217" s="1" t="n"/>
+      <c r="C217" s="1" t="n"/>
     </row>
     <row r="218">
-      <c r="D218" s="1" t="n"/>
+      <c r="C218" s="1" t="n"/>
     </row>
     <row r="219">
-      <c r="D219" s="1" t="n"/>
+      <c r="C219" s="1" t="n"/>
     </row>
     <row r="220">
-      <c r="D220" s="1" t="n"/>
+      <c r="C220" s="1" t="n"/>
     </row>
     <row r="221">
-      <c r="D221" s="1" t="n"/>
+      <c r="C221" s="1" t="n"/>
     </row>
     <row r="222">
-      <c r="D222" s="1" t="n"/>
+      <c r="C222" s="1" t="n"/>
     </row>
     <row r="223">
-      <c r="D223" s="1" t="n"/>
+      <c r="C223" s="1" t="n"/>
     </row>
     <row r="224">
-      <c r="D224" s="1" t="n"/>
+      <c r="C224" s="1" t="n"/>
     </row>
     <row r="225">
-      <c r="D225" s="1" t="n"/>
+      <c r="C225" s="1" t="n"/>
     </row>
     <row r="226">
-      <c r="D226" s="1" t="n"/>
+      <c r="C226" s="1" t="n"/>
     </row>
     <row r="227">
-      <c r="D227" s="1" t="n"/>
+      <c r="C227" s="1" t="n"/>
     </row>
     <row r="228">
-      <c r="D228" s="1" t="n"/>
+      <c r="C228" s="1" t="n"/>
     </row>
     <row r="229">
-      <c r="D229" s="1" t="n"/>
+      <c r="C229" s="1" t="n"/>
     </row>
     <row r="230">
-      <c r="D230" s="1" t="n"/>
+      <c r="C230" s="1" t="n"/>
     </row>
     <row r="231">
-      <c r="D231" s="1" t="n"/>
+      <c r="C231" s="1" t="n"/>
     </row>
     <row r="232">
-      <c r="D232" s="1" t="n"/>
+      <c r="C232" s="1" t="n"/>
     </row>
     <row r="233">
-      <c r="D233" s="1" t="n"/>
+      <c r="C233" s="1" t="n"/>
     </row>
     <row r="234">
-      <c r="D234" s="1" t="n"/>
+      <c r="C234" s="1" t="n"/>
     </row>
     <row r="235">
-      <c r="D235" s="1" t="n"/>
+      <c r="C235" s="1" t="n"/>
     </row>
     <row r="236">
-      <c r="D236" s="1" t="n"/>
+      <c r="C236" s="1" t="n"/>
     </row>
     <row r="237">
-      <c r="D237" s="1" t="n"/>
+      <c r="C237" s="1" t="n"/>
     </row>
     <row r="238">
-      <c r="D238" s="1" t="n"/>
+      <c r="C238" s="1" t="n"/>
     </row>
     <row r="239">
-      <c r="D239" s="1" t="n"/>
+      <c r="C239" s="1" t="n"/>
     </row>
     <row r="240">
-      <c r="D240" s="1" t="n"/>
+      <c r="C240" s="1" t="n"/>
     </row>
     <row r="241">
-      <c r="D241" s="1" t="n"/>
+      <c r="C241" s="1" t="n"/>
     </row>
     <row r="242">
-      <c r="D242" s="1" t="n"/>
+      <c r="C242" s="1" t="n"/>
     </row>
     <row r="243">
-      <c r="D243" s="1" t="n"/>
+      <c r="C243" s="1" t="n"/>
     </row>
     <row r="244">
-      <c r="D244" s="1" t="n"/>
+      <c r="C244" s="1" t="n"/>
     </row>
     <row r="245">
-      <c r="D245" s="1" t="n"/>
+      <c r="C245" s="1" t="n"/>
     </row>
     <row r="246">
-      <c r="D246" s="1" t="n"/>
+      <c r="C246" s="1" t="n"/>
     </row>
     <row r="247">
-      <c r="D247" s="1" t="n"/>
+      <c r="C247" s="1" t="n"/>
     </row>
     <row r="248">
-      <c r="D248" s="1" t="n"/>
+      <c r="C248" s="1" t="n"/>
     </row>
     <row r="249">
-      <c r="D249" s="1" t="n"/>
+      <c r="C249" s="1" t="n"/>
     </row>
     <row r="250">
-      <c r="D250" s="1" t="n"/>
+      <c r="C250" s="1" t="n"/>
     </row>
     <row r="251">
-      <c r="D251" s="1" t="n"/>
+      <c r="C251" s="1" t="n"/>
     </row>
     <row r="252">
-      <c r="D252" s="1" t="n"/>
+      <c r="C252" s="1" t="n"/>
     </row>
     <row r="253">
-      <c r="D253" s="1" t="n"/>
+      <c r="C253" s="1" t="n"/>
     </row>
     <row r="254">
-      <c r="D254" s="1" t="n"/>
+      <c r="C254" s="1" t="n"/>
     </row>
     <row r="255">
-      <c r="D255" s="1" t="n"/>
+      <c r="C255" s="1" t="n"/>
     </row>
     <row r="256">
-      <c r="D256" s="1" t="n"/>
+      <c r="C256" s="1" t="n"/>
     </row>
     <row r="257">
-      <c r="D257" s="1" t="n"/>
+      <c r="C257" s="1" t="n"/>
     </row>
     <row r="258">
-      <c r="D258" s="1" t="n"/>
+      <c r="C258" s="1" t="n"/>
     </row>
     <row r="259">
-      <c r="D259" s="1" t="n"/>
+      <c r="C259" s="1" t="n"/>
     </row>
     <row r="260">
-      <c r="D260" s="1" t="n"/>
+      <c r="C260" s="1" t="n"/>
     </row>
     <row r="261">
-      <c r="D261" s="1" t="n"/>
+      <c r="C261" s="1" t="n"/>
     </row>
     <row r="262">
-      <c r="D262" s="1" t="n"/>
+      <c r="C262" s="1" t="n"/>
     </row>
     <row r="263">
-      <c r="D263" s="1" t="n"/>
+      <c r="C263" s="1" t="n"/>
     </row>
     <row r="264">
-      <c r="D264" s="1" t="n"/>
+      <c r="C264" s="1" t="n"/>
     </row>
     <row r="265">
-      <c r="D265" s="1" t="n"/>
+      <c r="C265" s="1" t="n"/>
     </row>
     <row r="266">
-      <c r="D266" s="1" t="n"/>
+      <c r="C266" s="1" t="n"/>
     </row>
     <row r="267">
-      <c r="D267" s="1" t="n"/>
+      <c r="C267" s="1" t="n"/>
     </row>
     <row r="268">
-      <c r="D268" s="1" t="n"/>
+      <c r="C268" s="1" t="n"/>
     </row>
     <row r="269">
-      <c r="D269" s="1" t="n"/>
+      <c r="C269" s="1" t="n"/>
     </row>
     <row r="270">
-      <c r="D270" s="1" t="n"/>
+      <c r="C270" s="1" t="n"/>
     </row>
     <row r="271">
-      <c r="D271" s="1" t="n"/>
+      <c r="C271" s="1" t="n"/>
     </row>
     <row r="272">
-      <c r="D272" s="1" t="n"/>
+      <c r="C272" s="1" t="n"/>
     </row>
     <row r="273">
-      <c r="D273" s="1" t="n"/>
+      <c r="C273" s="1" t="n"/>
     </row>
     <row r="274">
-      <c r="D274" s="1" t="n"/>
+      <c r="C274" s="1" t="n"/>
     </row>
     <row r="275">
-      <c r="D275" s="1" t="n"/>
+      <c r="C275" s="1" t="n"/>
     </row>
     <row r="276">
-      <c r="D276" s="1" t="n"/>
+      <c r="C276" s="1" t="n"/>
     </row>
     <row r="277">
-      <c r="D277" s="1" t="n"/>
+      <c r="C277" s="1" t="n"/>
     </row>
     <row r="278">
-      <c r="D278" s="1" t="n"/>
+      <c r="C278" s="1" t="n"/>
     </row>
     <row r="279">
-      <c r="D279" s="1" t="n"/>
+      <c r="C279" s="1" t="n"/>
     </row>
     <row r="280">
-      <c r="D280" s="1" t="n"/>
+      <c r="C280" s="1" t="n"/>
     </row>
     <row r="281">
-      <c r="D281" s="1" t="n"/>
+      <c r="C281" s="1" t="n"/>
     </row>
     <row r="282">
-      <c r="D282" s="1" t="n"/>
+      <c r="C282" s="1" t="n"/>
     </row>
     <row r="283">
-      <c r="D283" s="1" t="n"/>
+      <c r="C283" s="1" t="n"/>
     </row>
     <row r="284">
-      <c r="D284" s="1" t="n"/>
+      <c r="C284" s="1" t="n"/>
     </row>
     <row r="285">
-      <c r="D285" s="1" t="n"/>
+      <c r="C285" s="1" t="n"/>
     </row>
     <row r="286">
-      <c r="D286" s="1" t="n"/>
+      <c r="C286" s="1" t="n"/>
     </row>
     <row r="287">
-      <c r="D287" s="1" t="n"/>
+      <c r="C287" s="1" t="n"/>
     </row>
     <row r="288">
-      <c r="D288" s="1" t="n"/>
+      <c r="C288" s="1" t="n"/>
     </row>
     <row r="289">
-      <c r="D289" s="1" t="n"/>
+      <c r="C289" s="1" t="n"/>
     </row>
     <row r="290">
-      <c r="D290" s="1" t="n"/>
+      <c r="C290" s="1" t="n"/>
     </row>
     <row r="291">
-      <c r="D291" s="1" t="n"/>
+      <c r="C291" s="1" t="n"/>
     </row>
     <row r="292">
-      <c r="D292" s="1" t="n"/>
+      <c r="C292" s="1" t="n"/>
     </row>
     <row r="293">
-      <c r="D293" s="1" t="n"/>
+      <c r="C293" s="1" t="n"/>
     </row>
     <row r="294">
-      <c r="D294" s="1" t="n"/>
+      <c r="C294" s="1" t="n"/>
     </row>
     <row r="295">
-      <c r="D295" s="1" t="n"/>
+      <c r="C295" s="1" t="n"/>
     </row>
     <row r="296">
-      <c r="D296" s="1" t="n"/>
+      <c r="C296" s="1" t="n"/>
     </row>
     <row r="297">
-      <c r="D297" s="1" t="n"/>
+      <c r="C297" s="1" t="n"/>
     </row>
     <row r="298">
-      <c r="D298" s="1" t="n"/>
+      <c r="C298" s="1" t="n"/>
     </row>
     <row r="299">
-      <c r="D299" s="1" t="n"/>
+      <c r="C299" s="1" t="n"/>
     </row>
     <row r="300">
-      <c r="D300" s="1" t="n"/>
+      <c r="C300" s="1" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="E2:E300" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Sexo" error="Elija Femenino o Masculino" type="list">
+    <dataValidation sqref="D2:D300" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Sexo" error="Elija Femenino o Masculino" type="list">
       <formula1>"Femenino,Masculino"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1645,7 +1620,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22.83203125" customWidth="1" min="1" max="1"/>
@@ -1740,19 +1715,19 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Nombres del estudiante.</t>
+          <t>Nombre completo en una sola celda. Escriba «Apellidos, Nombres» (con coma o punto y coma) para que el portal separe el apellido y ordene bien las listas. Sin coma, todo se guarda como nombre.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Ana María</t>
+          <t>Pérez Gómez, Ana María</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>apellidos</t>
+          <t>cedula</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1762,19 +1737,19 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Apellidos del estudiante.</t>
+          <t>Cédula del estudiante. Es su contraseña de entrada al portal; puede llevar guiones. No se repite. Mínimo 6 letras o números. La columna ya está en formato «Texto». Si el estudiante ya tiene acceso, puede dejarla vacía.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Pérez Gómez</t>
+          <t>8-123-456</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>cedula</t>
+          <t>sexo</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1784,19 +1759,19 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cédula del estudiante. Es su contraseña de entrada al portal; puede llevar guiones. No se repite. Mínimo 6 letras o números. La columna ya está en formato «Texto». Si el estudiante ya tiene acceso, puede dejarla vacía.</t>
+          <t>Elija Femenino o Masculino de la lista (también vale F o M). Si el estudiante ya tiene el sexo registrado, puede dejarla vacía.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8-123-456</t>
+          <t>Femenino</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>sexo</t>
+          <t>grado</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1806,19 +1781,19 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Elija Femenino o Masculino de la lista (también vale F o M). Si el estudiante ya tiene el sexo registrado, puede dejarla vacía.</t>
+          <t>Solo el número del grado (uno o dos dígitos).</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>9</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>grado</t>
+          <t>seccion</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1828,19 +1803,19 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Solo el número del grado (uno o dos dígitos).</t>
+          <t>Solo la letra de la sección. Grado 9 + sección C = grupo 9C.</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>C</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>seccion</t>
+          <t>anio_lectivo</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1850,41 +1825,41 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Solo la letra de la sección. Grado 9 + sección C = grupo 9C.</t>
+          <t>Año con cuatro cifras. Debe existir en Años lectivos.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>2027</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>anio_lectivo</t>
+          <t>correo_estudiante</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Año con cuatro cifras. Debe existir en Años lectivos.</t>
+          <t>Correo propio del estudiante, para invitarlo. No puede repetirse.</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>ana@example.com</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>correo_estudiante</t>
+          <t>nombre_acudiente</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1894,19 +1869,19 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Correo propio del estudiante, para invitarlo. No puede repetirse.</t>
+          <t>Nombre del acudiente.</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>ana@example.com</t>
+          <t>Carmen Gómez</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>nombre_acudiente</t>
+          <t>telefono_acudiente</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1916,19 +1891,19 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Nombre del acudiente.</t>
+          <t>Uno o varios teléfonos en la misma celda, separados por « / » o «; ».</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Carmen Gómez</t>
+          <t>6000-0001 / 6500-0002</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>telefono_acudiente</t>
+          <t>estado</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1938,32 +1913,10 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Uno o varios teléfonos en la misma celda, separados por « / » o «; ».</t>
+          <t>Estado de la matrícula. Vacío = activo.</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
-        <is>
-          <t>6000-0001 / 6500-0002</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>estado</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Estado de la matrícula. Vacío = activo.</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
         <is>
           <t>activo</t>
         </is>
